--- a/7RMartSuperMarketLatest/src/test/resources/TestData.xlsx
+++ b/7RMartSuperMarketLatest/src/test/resources/TestData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/reshmaunniktrishnan/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0B3EC7E-4C3E-DD42-B09C-88E8EFA70281}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D033446-913E-FE44-90FF-560BC9D17303}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="17260" activeTab="4" xr2:uid="{8204350D-4CDC-3D48-BFF6-BE033C23734B}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="17260" activeTab="3" xr2:uid="{8204350D-4CDC-3D48-BFF6-BE033C23734B}"/>
   </bookViews>
   <sheets>
     <sheet name="Loginpage" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="41">
   <si>
     <t>admin</t>
   </si>
@@ -128,9 +128,6 @@
     <t>Ram</t>
   </si>
   <si>
-    <t>ram@123</t>
-  </si>
-  <si>
     <t>Staff</t>
   </si>
   <si>
@@ -147,9 +144,6 @@
   </si>
   <si>
     <t>Reshma</t>
-  </si>
-  <si>
-    <t>resg$35</t>
   </si>
   <si>
     <t>Raju</t>
@@ -681,68 +675,50 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57579016-182F-244A-8915-6E982130CB93}">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>1</v>
       </c>
       <c r="B1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>27</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" t="s">
         <v>28</v>
       </c>
-      <c r="C2" t="s">
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
+      <c r="B3" t="s">
         <v>30</v>
       </c>
-      <c r="B3">
-        <v>1234</v>
-      </c>
-      <c r="C3" t="s">
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
         <v>34</v>
       </c>
-      <c r="B4" t="s">
-        <v>35</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="B5" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>36</v>
-      </c>
-      <c r="B5">
-        <v>12345</v>
-      </c>
-      <c r="C5" t="s">
-        <v>33</v>
-      </c>
-    </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1" xr:uid="{AD7FFA47-EBDA-0149-AFD4-E69702F8DA2C}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -754,13 +730,13 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1" t="s">
         <v>37</v>
-      </c>
-      <c r="B1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C1" t="s">
-        <v>39</v>
       </c>
       <c r="D1" t="s">
         <v>23</v>
@@ -768,16 +744,16 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C2">
         <v>123459</v>
       </c>
       <c r="D2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
